--- a/data/trans_camb/P43-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P43-Habitat-trans_camb.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -515,9 +515,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -529,25 +526,18 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -578,21 +568,6 @@
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>2023/2007</t>
         </is>
@@ -607,9 +582,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -624,17 +596,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11,69</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>14,34</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>17,46</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -648,21 +620,6 @@
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>17,46</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>11,69</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>14,34</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>17,46</t>
         </is>
@@ -677,47 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,31; 16,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>9,02; 19,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>12,9; 23,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,12; 17,0</t>
+          <t>6,31; 16,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,01; 19,57</t>
+          <t>9,02; 19,64</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,15; 22,36</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>6,12; 17,0</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>9,01; 19,57</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>12,15; 22,36</t>
+          <t>12,9; 23,02</t>
         </is>
       </c>
     </row>
@@ -730,17 +672,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -754,21 +696,6 @@
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>48,95%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>32,76%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>40,19%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>48,95%</t>
         </is>
@@ -783,47 +710,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>16,42; 51,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>23,23; 60,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>33,14; 69,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16,93; 51,82</t>
+          <t>16,42; 51,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23,97; 59,96</t>
+          <t>23,23; 60,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,72; 67,52</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>16,93; 51,82</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>23,97; 59,96</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>31,72; 67,52</t>
+          <t>33,14; 69,59</t>
         </is>
       </c>
     </row>
@@ -840,17 +752,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9,89</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>17,18</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>13,96</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -864,21 +776,6 @@
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>13,96</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>9,89</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>17,18</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>13,96</t>
         </is>
@@ -893,47 +790,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5,36; 14,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>12,66; 21,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>9,2; 18,72</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,63; 13,86</t>
+          <t>5,36; 14,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,6; 21,48</t>
+          <t>12,66; 21,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,54; 18,15</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>4,63; 13,86</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>12,6; 21,48</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>9,54; 18,15</t>
+          <t>9,2; 18,72</t>
         </is>
       </c>
     </row>
@@ -946,17 +828,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,55%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>39,45%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -970,21 +852,6 @@
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>39,45%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>27,95%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>48,55%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>39,45%</t>
         </is>
@@ -999,47 +866,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>14,3; 44,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>33,38; 65,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>23,81; 57,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,78; 43,09</t>
+          <t>14,3; 44,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>33,49; 65,17</t>
+          <t>33,38; 65,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,73; 54,48</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>12,78; 43,09</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>33,49; 65,17</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>24,73; 54,48</t>
+          <t>23,81; 57,06</t>
         </is>
       </c>
     </row>
@@ -1056,17 +908,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8,97</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4,83</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>30,32</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1080,21 +932,6 @@
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>30,32</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>8,97</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>4,83</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>30,32</t>
         </is>
@@ -1109,47 +946,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,97; 14,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,17; 10,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>15,09; 47,44</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,5; 14,04</t>
+          <t>3,97; 14,22</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 10,03</t>
+          <t>-0,17; 10,23</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,59; 48,46</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,5; 14,04</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-0,26; 10,03</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>15,59; 48,46</t>
+          <t>15,09; 47,44</t>
         </is>
       </c>
     </row>
@@ -1162,17 +984,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>77,9%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1186,21 +1008,6 @@
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>77,9%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>23,04%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>12,42%</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>77,9%</t>
         </is>
@@ -1215,47 +1022,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>9,28; 40,14</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,91; 28,03</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>37,72; 132,01</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8,31; 38,61</t>
+          <t>9,28; 40,14</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 27,82</t>
+          <t>-0,91; 28,03</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>38,63; 135,46</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>8,31; 38,61</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-0,72; 27,82</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>38,63; 135,46</t>
+          <t>37,72; 132,01</t>
         </is>
       </c>
     </row>
@@ -1272,17 +1064,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7,21</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10,83</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10,81</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1296,21 +1088,6 @@
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>10,81</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>7,21</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>10,83</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>10,81</t>
         </is>
@@ -1325,47 +1102,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,18; 11,29</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,24; 15,21</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,07; 17,05</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,19; 11,7</t>
+          <t>3,18; 11,29</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,48; 15,92</t>
+          <t>6,24; 15,21</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 17,53</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>3,19; 11,7</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>6,48; 15,92</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>-2,83; 17,53</t>
+          <t>-3,07; 17,05</t>
         </is>
       </c>
     </row>
@@ -1378,17 +1140,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1402,21 +1164,6 @@
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>26,31%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>17,55%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>26,37%</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>26,31%</t>
         </is>
@@ -1431,47 +1178,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,36; 29,25</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>14,52; 39,29</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-7,08; 42,65</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7,41; 30,29</t>
+          <t>7,36; 29,25</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>14,88; 40,72</t>
+          <t>14,52; 39,29</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-6,48; 44,04</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>7,41; 30,29</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>14,88; 40,72</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>-6,48; 44,04</t>
+          <t>-7,08; 42,65</t>
         </is>
       </c>
     </row>
@@ -1488,17 +1220,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9,24</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12,02</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>18,02</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1512,21 +1244,6 @@
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>18,02</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>9,24</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>12,02</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>18,02</t>
         </is>
@@ -1541,47 +1258,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,9; 11,84</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>9,6; 14,42</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>12,85; 28,58</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6,75; 11,59</t>
+          <t>6,9; 11,84</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9,4; 14,29</t>
+          <t>9,6; 14,42</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,12; 28,66</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>6,75; 11,59</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>9,4; 14,29</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>13,12; 28,66</t>
+          <t>12,85; 28,58</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1296,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,53%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1618,21 +1320,6 @@
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>47,53%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>24,37%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>31,72%</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>47,53%</t>
         </is>
@@ -1647,47 +1334,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>17,47; 32,11</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>24,39; 39,4</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>32,93; 75,01</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>17,24; 31,67</t>
+          <t>17,47; 32,11</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>23,98; 39,03</t>
+          <t>24,39; 39,4</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>34,13; 77,23</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>17,24; 31,67</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>23,98; 39,03</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>34,13; 77,23</t>
+          <t>32,93; 75,01</t>
         </is>
       </c>
     </row>
@@ -1699,13 +1371,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="8">
     <mergeCell ref="A4:A7"/>
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A12:A15"/>
-    <mergeCell ref="I1:K1"/>
     <mergeCell ref="A20:A23"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="A16:A19"/>

--- a/data/trans_camb/P43-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P43-Habitat-trans_camb.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17,46</t>
+          <t>16,64</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,46</t>
+          <t>16,64</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,31; 16,66</t>
+          <t>6,19; 16,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,02; 19,64</t>
+          <t>9,18; 19,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,9; 23,02</t>
+          <t>11,35; 21,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,31; 16,66</t>
+          <t>6,19; 16,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,02; 19,64</t>
+          <t>9,18; 19,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,9; 23,02</t>
+          <t>11,35; 21,54</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>46,64%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>46,64%</t>
         </is>
       </c>
     </row>
@@ -710,32 +710,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,42; 51,34</t>
+          <t>16,65; 51,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>23,23; 60,09</t>
+          <t>24,91; 61,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33,14; 69,59</t>
+          <t>29,51; 65,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16,42; 51,34</t>
+          <t>16,65; 51,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23,23; 60,09</t>
+          <t>24,91; 61,32</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,14; 69,59</t>
+          <t>29,51; 65,79</t>
         </is>
       </c>
     </row>
@@ -762,7 +762,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13,96</t>
+          <t>13,57</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,96</t>
+          <t>13,57</t>
         </is>
       </c>
     </row>
@@ -790,32 +790,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,36; 14,26</t>
+          <t>5,47; 14,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,66; 21,91</t>
+          <t>12,99; 21,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,2; 18,72</t>
+          <t>9,04; 17,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,36; 14,26</t>
+          <t>5,47; 14,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,66; 21,91</t>
+          <t>12,99; 21,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,2; 18,72</t>
+          <t>9,04; 17,63</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>38,36%</t>
         </is>
       </c>
     </row>
@@ -866,32 +866,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,3; 44,18</t>
+          <t>14,11; 43,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>33,38; 65,76</t>
+          <t>33,85; 65,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23,81; 57,06</t>
+          <t>24,36; 54,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14,3; 44,18</t>
+          <t>14,11; 43,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>33,38; 65,76</t>
+          <t>33,85; 65,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,81; 57,06</t>
+          <t>24,36; 54,24</t>
         </is>
       </c>
     </row>
@@ -918,7 +918,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>30,32</t>
+          <t>13,17</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>30,32</t>
+          <t>13,17</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,97; 14,22</t>
+          <t>3,49; 14,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 10,23</t>
+          <t>-0,46; 9,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,09; 47,44</t>
+          <t>7,7; 18,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,97; 14,22</t>
+          <t>3,49; 14,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 10,23</t>
+          <t>-0,46; 9,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,09; 47,44</t>
+          <t>7,7; 18,25</t>
         </is>
       </c>
     </row>
@@ -994,7 +994,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>77,9%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,9%</t>
+          <t>33,83%</t>
         </is>
       </c>
     </row>
@@ -1022,32 +1022,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9,28; 40,14</t>
+          <t>8,23; 38,05</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 28,03</t>
+          <t>-1,3; 26,84</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>37,72; 132,01</t>
+          <t>18,56; 50,61</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9,28; 40,14</t>
+          <t>8,23; 38,05</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 28,03</t>
+          <t>-1,3; 26,84</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>37,72; 132,01</t>
+          <t>18,56; 50,61</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10,81</t>
+          <t>14,62</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,81</t>
+          <t>14,62</t>
         </is>
       </c>
     </row>
@@ -1102,32 +1102,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,18; 11,29</t>
+          <t>2,84; 11,65</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,24; 15,21</t>
+          <t>6,21; 15,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 17,05</t>
+          <t>9,81; 18,47</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,18; 11,29</t>
+          <t>2,84; 11,65</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,24; 15,21</t>
+          <t>6,21; 15,38</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 17,05</t>
+          <t>9,81; 18,47</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>35,59%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>35,59%</t>
         </is>
       </c>
     </row>
@@ -1178,32 +1178,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,36; 29,25</t>
+          <t>6,5; 30,46</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>14,52; 39,29</t>
+          <t>14,17; 39,08</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-7,08; 42,65</t>
+          <t>22,64; 48,19</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7,36; 29,25</t>
+          <t>6,5; 30,46</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>14,52; 39,29</t>
+          <t>14,17; 39,08</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-7,08; 42,65</t>
+          <t>22,64; 48,19</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>18,02</t>
+          <t>14,42</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,02</t>
+          <t>14,42</t>
         </is>
       </c>
     </row>
@@ -1258,32 +1258,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6,9; 11,84</t>
+          <t>6,91; 11,76</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9,6; 14,42</t>
+          <t>9,69; 14,52</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12,85; 28,58</t>
+          <t>12,16; 16,83</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6,9; 11,84</t>
+          <t>6,91; 11,76</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9,6; 14,42</t>
+          <t>9,69; 14,52</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,85; 28,58</t>
+          <t>12,16; 16,83</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>38,03%</t>
         </is>
       </c>
     </row>
@@ -1334,32 +1334,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>17,47; 32,11</t>
+          <t>17,55; 31,96</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>24,39; 39,4</t>
+          <t>24,93; 39,65</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>32,93; 75,01</t>
+          <t>30,88; 45,91</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>17,47; 32,11</t>
+          <t>17,55; 31,96</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>24,39; 39,4</t>
+          <t>24,93; 39,65</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>32,93; 75,01</t>
+          <t>30,88; 45,91</t>
         </is>
       </c>
     </row>
